--- a/tests/fixtures/06_merged_cells/pattern.xlsx
+++ b/tests/fixtures/06_merged_cells/pattern.xlsx
@@ -694,7 +694,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>table:1</t>
+          <t>table:*</t>
         </is>
       </c>
     </row>
